--- a/src/data/Time_Trials.xlsx
+++ b/src/data/Time_Trials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wartburgedu.sharepoint.com/sites/XC/Shared Documents/General/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huttonedney/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB31EA27-2B1F-4E23-96C5-A8D8BFD8EE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B96091D1-4C0A-D844-9BE7-32CB5EBFB1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="6" xr2:uid="{157AA48F-6886-479E-9AFA-798C4A5D7E17}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23240" windowHeight="12200" xr2:uid="{157AA48F-6886-479E-9AFA-798C4A5D7E17}"/>
   </bookViews>
   <sheets>
     <sheet name="MidD" sheetId="6" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="275">
   <si>
     <t>Name</t>
   </si>
@@ -692,16 +692,112 @@
     <t>Griffin Steiniger</t>
   </si>
   <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>pr</t>
+  </si>
+  <si>
+    <t>Sydney Bochmann</t>
+  </si>
+  <si>
+    <t>Ava Vance</t>
+  </si>
+  <si>
+    <t>Ryle Bainbridge</t>
+  </si>
+  <si>
+    <t>Bella Skay</t>
+  </si>
+  <si>
+    <t>Kam Sherwood</t>
+  </si>
+  <si>
+    <t>Jacob Vanderwilt</t>
+  </si>
+  <si>
+    <t>Ben Roussell</t>
+  </si>
+  <si>
+    <t>David Williams</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>700</t>
+  </si>
+  <si>
+    <t>1100</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>1k</t>
+  </si>
+  <si>
+    <t>2k</t>
+  </si>
+  <si>
+    <t>3k</t>
+  </si>
+  <si>
+    <t>4k</t>
+  </si>
+  <si>
+    <t>5k</t>
+  </si>
+  <si>
+    <t>Tyler Schermerhorn</t>
+  </si>
+  <si>
+    <t>All-Ducky</t>
+  </si>
+  <si>
+    <t>Ducky Champion</t>
+  </si>
+  <si>
+    <t>Nich Henry</t>
+  </si>
+  <si>
+    <t>Drake Strnad</t>
+  </si>
+  <si>
+    <t>Will Howes</t>
+  </si>
+  <si>
+    <t>Kaleb Grant</t>
+  </si>
+  <si>
+    <t>Cayden Schellhorn</t>
+  </si>
+  <si>
+    <t>Riley Mayer</t>
+  </si>
+  <si>
+    <t>Vic Breitbach</t>
+  </si>
+  <si>
+    <t>Miricle Corbo</t>
+  </si>
+  <si>
+    <t>Leah Cherry</t>
+  </si>
+  <si>
+    <t>Allegra Knudson</t>
+  </si>
+  <si>
     <t>Heat</t>
   </si>
   <si>
-    <t>Column1</t>
+    <t>Janae Hansen</t>
   </si>
   <si>
     <t>Haley Meyer</t>
   </si>
   <si>
-    <t>Janae Hansen</t>
+    <t>Marissa Pewe</t>
   </si>
   <si>
     <t>Meghan Zopel</t>
@@ -710,70 +806,13 @@
     <t>Logan Rosas</t>
   </si>
   <si>
-    <t>Marissa Pewe</t>
-  </si>
-  <si>
-    <t>Sydney Bochmann</t>
-  </si>
-  <si>
-    <t>pr</t>
-  </si>
-  <si>
-    <t>Ava Vance</t>
-  </si>
-  <si>
-    <t>Ryle Bainbridge</t>
-  </si>
-  <si>
-    <t>Bella Skay</t>
-  </si>
-  <si>
-    <t>Kam Sherwood</t>
-  </si>
-  <si>
-    <t>Jacob Vanderwilt</t>
-  </si>
-  <si>
-    <t>Ben Roussell</t>
-  </si>
-  <si>
-    <t>David Williams</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>700</t>
-  </si>
-  <si>
-    <t>1100</t>
-  </si>
-  <si>
-    <t>1500</t>
-  </si>
-  <si>
-    <t>1k</t>
-  </si>
-  <si>
-    <t>2k</t>
-  </si>
-  <si>
-    <t>3k</t>
-  </si>
-  <si>
-    <t>4k</t>
-  </si>
-  <si>
-    <t>5k</t>
-  </si>
-  <si>
-    <t>Tyler Schermerhorn</t>
-  </si>
-  <si>
-    <t>All-Ducky</t>
-  </si>
-  <si>
-    <t>Ducky Champion</t>
+    <t>Sam Rew</t>
+  </si>
+  <si>
+    <t>Sydney Bochman</t>
+  </si>
+  <si>
+    <t>Taylor Burns</t>
   </si>
   <si>
     <t>Evan Richardson</t>
@@ -782,48 +821,9 @@
     <t>Lydia Maas</t>
   </si>
   <si>
-    <t>Nich Henry</t>
-  </si>
-  <si>
     <t>Mia</t>
   </si>
   <si>
-    <t>Drake Strnad</t>
-  </si>
-  <si>
-    <t>Will Howes</t>
-  </si>
-  <si>
-    <t>Kaleb Grant</t>
-  </si>
-  <si>
-    <t>Cayden Schellhorn</t>
-  </si>
-  <si>
-    <t>Riley Mayer</t>
-  </si>
-  <si>
-    <t>Vic Breitbach</t>
-  </si>
-  <si>
-    <t>Sam Rew</t>
-  </si>
-  <si>
-    <t>Sydney Bochman</t>
-  </si>
-  <si>
-    <t>Miricle Corbo</t>
-  </si>
-  <si>
-    <t>Taylor Burns</t>
-  </si>
-  <si>
-    <t>Leah Cherry</t>
-  </si>
-  <si>
-    <t>Allegra Knudson</t>
-  </si>
-  <si>
     <t>Henry Nichols</t>
   </si>
   <si>
@@ -864,6 +864,9 @@
   </si>
   <si>
     <t>Toben Edney</t>
+  </si>
+  <si>
+    <t>Lillyan Kiehne</t>
   </si>
 </sst>
 </file>
@@ -875,7 +878,7 @@
     <numFmt numFmtId="165" formatCode="m:ss.00"/>
     <numFmt numFmtId="166" formatCode="mm:ss.0;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,6 +917,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Garamond"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1110,13 +1114,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
@@ -1138,6 +1135,13 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1266,13 +1270,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
@@ -1291,6 +1288,13 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1939,13 +1943,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
@@ -1967,6 +1964,13 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2095,13 +2099,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
         </left>
@@ -2123,6 +2120,13 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2162,8 +2166,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{64561B06-5BFF-4E7F-B02F-610511AE2474}" name="Table19" displayName="Table19" ref="A1:C11" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64" headerRowBorderDxfId="62" tableBorderDxfId="63" totalsRowBorderDxfId="61">
-  <autoFilter ref="A1:C11" xr:uid="{64561B06-5BFF-4E7F-B02F-610511AE2474}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{64561B06-5BFF-4E7F-B02F-610511AE2474}" name="Table19" displayName="Table19" ref="A1:C16" totalsRowShown="0" headerRowDxfId="65" dataDxfId="63" headerRowBorderDxfId="64" tableBorderDxfId="62" totalsRowBorderDxfId="61">
+  <autoFilter ref="A1:C16" xr:uid="{64561B06-5BFF-4E7F-B02F-610511AE2474}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{26D0FC73-7B67-443F-BB3C-9CED56E69937}" name="Name" dataDxfId="60"/>
     <tableColumn id="2" xr3:uid="{5AF55AEC-F4F3-427F-B983-B8B5CC982724}" name="Time" dataDxfId="59"/>
@@ -2311,7 +2315,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{F979CED4-F8C2-42AB-AF0F-81DA5EF4E3CF}" name="Table15" displayName="Table15" ref="F1:H25" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{F979CED4-F8C2-42AB-AF0F-81DA5EF4E3CF}" name="Table15" displayName="Table15" ref="F1:H25" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <autoFilter ref="F1:H25" xr:uid="{F979CED4-F8C2-42AB-AF0F-81DA5EF4E3CF}">
     <filterColumn colId="2">
       <filters>
@@ -2332,7 +2336,7 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{99084FBF-3345-46C2-B5B0-C108F138E1E5}" name="Table20" displayName="Table20" ref="A1:C29" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{99084FBF-3345-46C2-B5B0-C108F138E1E5}" name="Table20" displayName="Table20" ref="A1:C29" totalsRowShown="0" headerRowDxfId="7" dataDxfId="5" headerRowBorderDxfId="6" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="A1:C29" xr:uid="{99084FBF-3345-46C2-B5B0-C108F138E1E5}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1958DDC9-8C27-4A75-B7CA-4825B548C3FD}" name="Name" dataDxfId="2"/>
@@ -2344,8 +2348,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{93ECE94F-40E9-41AE-883E-7C51483A6E63}" name="Table1919" displayName="Table1919" ref="E1:G5" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56" headerRowBorderDxfId="54" tableBorderDxfId="55" totalsRowBorderDxfId="53">
-  <autoFilter ref="E1:G5" xr:uid="{93ECE94F-40E9-41AE-883E-7C51483A6E63}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{93ECE94F-40E9-41AE-883E-7C51483A6E63}" name="Table1919" displayName="Table1919" ref="E1:G8" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53">
+  <autoFilter ref="E1:G8" xr:uid="{93ECE94F-40E9-41AE-883E-7C51483A6E63}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{05F225E6-C1D5-41A5-973A-32794EDC0CCC}" name="Name" dataDxfId="52"/>
     <tableColumn id="2" xr3:uid="{BF295A11-2DDB-4F07-92CA-668599884584}" name="Time" dataDxfId="51"/>
@@ -2473,9 +2477,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2513,7 +2517,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2619,7 +2623,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2761,7 +2765,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2769,14 +2773,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB8BE9C-834A-4653-BD1F-19CB7BE343E0}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2796,151 +2800,262 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B2" s="9">
-        <v>2.9995370370370375E-3</v>
+        <v>2.9591435185185185E-3</v>
       </c>
       <c r="C2" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F2" s="9">
-        <v>3.7846064814814817E-3</v>
+        <v>3.6651620370370371E-3</v>
       </c>
       <c r="G2" s="8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>5</v>
+        <v>253</v>
       </c>
       <c r="B3" s="9">
-        <v>3.027546296296296E-3</v>
+        <v>2.9707175925925929E-3</v>
       </c>
       <c r="C3" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F3" s="9">
+        <v>3.6883101851851855E-3</v>
+      </c>
+      <c r="G3" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9">
+        <v>2.9995370370370375E-3</v>
+      </c>
+      <c r="C4" s="8">
+        <v>2025</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="9">
+        <v>3.7846064814814817E-3</v>
+      </c>
+      <c r="G4" s="8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="9">
+        <v>3.027546296296296E-3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>2025</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="9">
         <v>3.794444444444444E-3</v>
       </c>
-      <c r="G3" s="8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="8" t="s">
+      <c r="G5" s="8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B6" s="9">
         <v>3.0540509259259258E-3</v>
       </c>
-      <c r="C4" s="8">
-        <v>2025</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="C6" s="8">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F6" s="9">
         <v>3.854398148148148E-3</v>
       </c>
-      <c r="G4" s="8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="8" t="s">
+      <c r="G6" s="8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="9">
+        <v>3.0555555555555557E-3</v>
+      </c>
+      <c r="C7" s="8">
+        <v>2026</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="F7" s="9">
+        <v>3.9892361111111109E-3</v>
+      </c>
+      <c r="G7" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B8" s="9">
         <v>3.0585648148148147E-3</v>
       </c>
-      <c r="C5" s="8">
-        <v>2025</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="C8" s="8">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F8" s="9">
         <v>4.2981481481481482E-3</v>
       </c>
-      <c r="G5" s="8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="8" t="s">
+      <c r="G8" s="8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B9" s="9">
         <v>3.1074074074074077E-3</v>
       </c>
-      <c r="C6" s="8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="8" t="s">
+      <c r="C9" s="8">
+        <v>2025</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B10" s="9">
         <v>3.1101851851851854E-3</v>
       </c>
-      <c r="C7" s="8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="8" t="s">
+      <c r="C10" s="8">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B11" s="9">
         <v>3.1153935185185186E-3</v>
       </c>
-      <c r="C8" s="8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="8" t="s">
+      <c r="C11" s="8">
+        <v>2025</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B12" s="9">
         <v>3.1531250000000001E-3</v>
       </c>
-      <c r="C9" s="8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="8" t="s">
+      <c r="C12" s="8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B13" s="9">
         <v>3.1579861111111114E-3</v>
       </c>
-      <c r="C10" s="8">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="8" t="s">
+      <c r="C13" s="8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" s="9">
+        <v>3.2021990740740743E-3</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B15" s="9">
         <v>3.4386574074074076E-3</v>
       </c>
-      <c r="C11" s="8">
-        <v>2025</v>
-      </c>
+      <c r="C15" s="8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="9">
+        <v>3.4684027777777782E-3</v>
+      </c>
+      <c r="C16" s="8">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2954,16 +3069,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872D61C7-5E7F-48D7-8170-00944401C5CA}">
   <dimension ref="A1:G279"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.1640625" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2983,7 +3098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -3003,7 +3118,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -3023,7 +3138,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -3043,7 +3158,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -3063,7 +3178,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -3083,7 +3198,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -3103,7 +3218,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -3123,7 +3238,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -3143,7 +3258,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -3163,7 +3278,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -3183,7 +3298,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3203,7 +3318,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -3223,7 +3338,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
@@ -3243,7 +3358,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -3263,7 +3378,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
@@ -3283,7 +3398,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -3303,7 +3418,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>46</v>
       </c>
@@ -3323,7 +3438,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -3343,7 +3458,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>50</v>
       </c>
@@ -3363,7 +3478,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -3383,7 +3498,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -3403,7 +3518,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
@@ -3423,7 +3538,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>52</v>
       </c>
@@ -3443,7 +3558,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -3463,7 +3578,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>60</v>
       </c>
@@ -3483,7 +3598,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>62</v>
       </c>
@@ -3503,7 +3618,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -3523,7 +3638,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -3543,7 +3658,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -3563,7 +3678,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -3583,7 +3698,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
@@ -3603,7 +3718,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>71</v>
       </c>
@@ -3623,7 +3738,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>72</v>
       </c>
@@ -3643,7 +3758,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>74</v>
       </c>
@@ -3663,7 +3778,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>76</v>
       </c>
@@ -3683,7 +3798,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -3703,7 +3818,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -3723,7 +3838,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>79</v>
       </c>
@@ -3743,7 +3858,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>80</v>
       </c>
@@ -3763,7 +3878,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>82</v>
       </c>
@@ -3783,7 +3898,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>84</v>
       </c>
@@ -3803,7 +3918,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -3823,7 +3938,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -3843,7 +3958,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>71</v>
       </c>
@@ -3863,7 +3978,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>68</v>
       </c>
@@ -3883,7 +3998,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>87</v>
       </c>
@@ -3903,7 +4018,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>89</v>
       </c>
@@ -3923,7 +4038,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -3943,7 +4058,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>64</v>
       </c>
@@ -3963,7 +4078,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>92</v>
       </c>
@@ -3983,7 +4098,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>94</v>
       </c>
@@ -4003,7 +4118,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>79</v>
       </c>
@@ -4023,7 +4138,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>96</v>
       </c>
@@ -4043,7 +4158,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>87</v>
       </c>
@@ -4063,7 +4178,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>66</v>
       </c>
@@ -4083,7 +4198,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -4103,7 +4218,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>89</v>
       </c>
@@ -4123,7 +4238,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>59</v>
       </c>
@@ -4143,7 +4258,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>101</v>
       </c>
@@ -4163,7 +4278,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>22</v>
       </c>
@@ -4183,7 +4298,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>84</v>
       </c>
@@ -4203,7 +4318,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>64</v>
       </c>
@@ -4223,7 +4338,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>104</v>
       </c>
@@ -4243,7 +4358,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -4263,7 +4378,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>105</v>
       </c>
@@ -4283,7 +4398,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -4303,7 +4418,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>107</v>
       </c>
@@ -4323,7 +4438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>50</v>
       </c>
@@ -4343,7 +4458,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>109</v>
       </c>
@@ -4363,7 +4478,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>111</v>
       </c>
@@ -4383,7 +4498,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>74</v>
       </c>
@@ -4403,7 +4518,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>113</v>
       </c>
@@ -4423,7 +4538,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>115</v>
       </c>
@@ -4443,7 +4558,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>92</v>
       </c>
@@ -4463,7 +4578,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>117</v>
       </c>
@@ -4483,7 +4598,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>118</v>
       </c>
@@ -4503,7 +4618,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>8</v>
       </c>
@@ -4523,7 +4638,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>120</v>
       </c>
@@ -4543,7 +4658,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>79</v>
       </c>
@@ -4563,7 +4678,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>122</v>
       </c>
@@ -4583,7 +4698,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>71</v>
       </c>
@@ -4603,7 +4718,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>124</v>
       </c>
@@ -4623,7 +4738,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>125</v>
       </c>
@@ -4643,7 +4758,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>126</v>
       </c>
@@ -4663,7 +4778,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>120</v>
       </c>
@@ -4683,7 +4798,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>111</v>
       </c>
@@ -4703,7 +4818,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>107</v>
       </c>
@@ -4723,7 +4838,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>129</v>
       </c>
@@ -4743,7 +4858,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>117</v>
       </c>
@@ -4763,7 +4878,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>80</v>
       </c>
@@ -4783,7 +4898,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>132</v>
       </c>
@@ -4803,7 +4918,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>107</v>
       </c>
@@ -4823,7 +4938,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>129</v>
       </c>
@@ -4843,7 +4958,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -4863,7 +4978,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>117</v>
       </c>
@@ -4883,7 +4998,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -4903,7 +5018,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>80</v>
       </c>
@@ -4923,7 +5038,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>129</v>
       </c>
@@ -4943,7 +5058,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>136</v>
       </c>
@@ -4963,7 +5078,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>138</v>
       </c>
@@ -4983,7 +5098,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>139</v>
       </c>
@@ -5003,7 +5118,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>74</v>
       </c>
@@ -5023,7 +5138,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>141</v>
       </c>
@@ -5043,7 +5158,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>142</v>
       </c>
@@ -5063,7 +5178,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>144</v>
       </c>
@@ -5083,7 +5198,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>146</v>
       </c>
@@ -5103,7 +5218,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>132</v>
       </c>
@@ -5123,7 +5238,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>48</v>
       </c>
@@ -5143,7 +5258,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>149</v>
       </c>
@@ -5163,7 +5278,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>150</v>
       </c>
@@ -5183,7 +5298,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>152</v>
       </c>
@@ -5203,7 +5318,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>124</v>
       </c>
@@ -5223,7 +5338,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>136</v>
       </c>
@@ -5243,7 +5358,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>136</v>
       </c>
@@ -5263,7 +5378,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>154</v>
       </c>
@@ -5283,7 +5398,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>155</v>
       </c>
@@ -5303,7 +5418,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>136</v>
       </c>
@@ -5323,7 +5438,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>124</v>
       </c>
@@ -5343,7 +5458,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>136</v>
       </c>
@@ -5363,7 +5478,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>160</v>
       </c>
@@ -5383,7 +5498,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>162</v>
       </c>
@@ -5403,7 +5518,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>164</v>
       </c>
@@ -5423,7 +5538,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E124" t="s">
         <v>39</v>
       </c>
@@ -5434,7 +5549,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E125" t="s">
         <v>61</v>
       </c>
@@ -5445,7 +5560,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E126" t="s">
         <v>88</v>
       </c>
@@ -5456,7 +5571,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E127" t="s">
         <v>166</v>
       </c>
@@ -5467,7 +5582,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E128" t="s">
         <v>166</v>
       </c>
@@ -5478,7 +5593,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="129" spans="5:7" hidden="1">
+    <row r="129" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E129" t="s">
         <v>119</v>
       </c>
@@ -5489,7 +5604,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="130" spans="5:7" hidden="1">
+    <row r="130" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E130" t="s">
         <v>167</v>
       </c>
@@ -5500,7 +5615,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="131" spans="5:7" hidden="1">
+    <row r="131" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E131" t="s">
         <v>168</v>
       </c>
@@ -5511,7 +5626,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="132" spans="5:7" hidden="1">
+    <row r="132" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E132" t="s">
         <v>88</v>
       </c>
@@ -5522,7 +5637,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="133" spans="5:7">
+    <row r="133" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E133" t="s">
         <v>169</v>
       </c>
@@ -5533,7 +5648,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="134" spans="5:7" hidden="1">
+    <row r="134" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E134" t="s">
         <v>12</v>
       </c>
@@ -5544,7 +5659,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="135" spans="5:7" hidden="1">
+    <row r="135" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E135" t="s">
         <v>170</v>
       </c>
@@ -5555,7 +5670,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="136" spans="5:7" hidden="1">
+    <row r="136" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E136" t="s">
         <v>99</v>
       </c>
@@ -5566,7 +5681,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="137" spans="5:7">
+    <row r="137" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E137" t="s">
         <v>171</v>
       </c>
@@ -5577,7 +5692,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="138" spans="5:7" hidden="1">
+    <row r="138" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E138" t="s">
         <v>172</v>
       </c>
@@ -5588,7 +5703,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="139" spans="5:7" hidden="1">
+    <row r="139" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E139" t="s">
         <v>145</v>
       </c>
@@ -5599,7 +5714,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="140" spans="5:7" hidden="1">
+    <row r="140" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E140" t="s">
         <v>157</v>
       </c>
@@ -5610,7 +5725,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="141" spans="5:7" hidden="1">
+    <row r="141" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E141" t="s">
         <v>159</v>
       </c>
@@ -5621,7 +5736,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="142" spans="5:7">
+    <row r="142" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E142" t="s">
         <v>173</v>
       </c>
@@ -5632,7 +5747,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="143" spans="5:7" hidden="1">
+    <row r="143" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E143" t="s">
         <v>47</v>
       </c>
@@ -5643,7 +5758,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="144" spans="5:7" hidden="1">
+    <row r="144" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E144" t="s">
         <v>97</v>
       </c>
@@ -5654,7 +5769,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="145" spans="5:7" hidden="1">
+    <row r="145" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E145" t="s">
         <v>148</v>
       </c>
@@ -5665,7 +5780,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="146" spans="5:7" hidden="1">
+    <row r="146" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E146" t="s">
         <v>174</v>
       </c>
@@ -5676,7 +5791,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="147" spans="5:7" hidden="1">
+    <row r="147" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E147" t="s">
         <v>102</v>
       </c>
@@ -5687,7 +5802,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="148" spans="5:7">
+    <row r="148" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E148" t="s">
         <v>175</v>
       </c>
@@ -5698,7 +5813,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="149" spans="5:7" hidden="1">
+    <row r="149" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E149" s="1" t="s">
         <v>112</v>
       </c>
@@ -5709,7 +5824,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="150" spans="5:7">
+    <row r="150" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E150" t="s">
         <v>177</v>
       </c>
@@ -5720,7 +5835,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="151" spans="5:7" hidden="1">
+    <row r="151" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E151" t="s">
         <v>170</v>
       </c>
@@ -5731,7 +5846,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="152" spans="5:7" hidden="1">
+    <row r="152" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E152" t="s">
         <v>153</v>
       </c>
@@ -5742,7 +5857,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="153" spans="5:7" hidden="1">
+    <row r="153" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E153" t="s">
         <v>178</v>
       </c>
@@ -5753,7 +5868,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="154" spans="5:7" hidden="1">
+    <row r="154" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E154" t="s">
         <v>179</v>
       </c>
@@ -5764,7 +5879,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="155" spans="5:7" hidden="1">
+    <row r="155" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E155" t="s">
         <v>180</v>
       </c>
@@ -5775,7 +5890,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="156" spans="5:7" hidden="1">
+    <row r="156" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E156" t="s">
         <v>181</v>
       </c>
@@ -5786,7 +5901,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="157" spans="5:7" hidden="1">
+    <row r="157" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E157" t="s">
         <v>182</v>
       </c>
@@ -5797,7 +5912,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="158" spans="5:7" hidden="1">
+    <row r="158" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E158" t="s">
         <v>131</v>
       </c>
@@ -5808,7 +5923,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="159" spans="5:7" hidden="1">
+    <row r="159" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E159" t="s">
         <v>153</v>
       </c>
@@ -5819,7 +5934,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="160" spans="5:7" hidden="1">
+    <row r="160" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E160" t="s">
         <v>128</v>
       </c>
@@ -5830,7 +5945,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="161" spans="5:7" hidden="1">
+    <row r="161" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E161" t="s">
         <v>134</v>
       </c>
@@ -5841,7 +5956,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="162" spans="5:7" hidden="1">
+    <row r="162" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E162" s="1" t="s">
         <v>12</v>
       </c>
@@ -5852,7 +5967,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="163" spans="5:7" hidden="1">
+    <row r="163" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E163" t="s">
         <v>90</v>
       </c>
@@ -5863,7 +5978,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="164" spans="5:7" hidden="1">
+    <row r="164" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E164" t="s">
         <v>5</v>
       </c>
@@ -5874,7 +5989,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="165" spans="5:7">
+    <row r="165" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E165" t="s">
         <v>11</v>
       </c>
@@ -5885,7 +6000,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="166" spans="5:7" hidden="1">
+    <row r="166" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E166" t="s">
         <v>167</v>
       </c>
@@ -5896,7 +6011,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="167" spans="5:7" hidden="1">
+    <row r="167" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E167" t="s">
         <v>77</v>
       </c>
@@ -5907,7 +6022,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="168" spans="5:7" hidden="1">
+    <row r="168" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E168" t="s">
         <v>183</v>
       </c>
@@ -5918,7 +6033,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="169" spans="5:7" hidden="1">
+    <row r="169" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E169" t="s">
         <v>81</v>
       </c>
@@ -5929,7 +6044,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="170" spans="5:7" hidden="1">
+    <row r="170" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E170" s="1" t="s">
         <v>131</v>
       </c>
@@ -5940,7 +6055,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="5:7" hidden="1">
+    <row r="171" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E171" s="1" t="s">
         <v>90</v>
       </c>
@@ -5951,7 +6066,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="172" spans="5:7" hidden="1">
+    <row r="172" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E172" t="s">
         <v>100</v>
       </c>
@@ -5962,7 +6077,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="173" spans="5:7" hidden="1">
+    <row r="173" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E173" s="1" t="s">
         <v>110</v>
       </c>
@@ -5973,7 +6088,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="174" spans="5:7" hidden="1">
+    <row r="174" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E174" t="s">
         <v>12</v>
       </c>
@@ -5984,7 +6099,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="175" spans="5:7" hidden="1">
+    <row r="175" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E175" t="s">
         <v>135</v>
       </c>
@@ -5995,7 +6110,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="176" spans="5:7" hidden="1">
+    <row r="176" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E176" t="s">
         <v>112</v>
       </c>
@@ -6006,7 +6121,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="177" spans="5:7" hidden="1">
+    <row r="177" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E177" s="1" t="s">
         <v>159</v>
       </c>
@@ -6017,7 +6132,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="178" spans="5:7" hidden="1">
+    <row r="178" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E178" s="1" t="s">
         <v>184</v>
       </c>
@@ -6028,7 +6143,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="179" spans="5:7">
+    <row r="179" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E179" t="s">
         <v>13</v>
       </c>
@@ -6039,7 +6154,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="180" spans="5:7">
+    <row r="180" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E180" t="s">
         <v>185</v>
       </c>
@@ -6050,7 +6165,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="181" spans="5:7" hidden="1">
+    <row r="181" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E181" t="s">
         <v>57</v>
       </c>
@@ -6061,7 +6176,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="182" spans="5:7" hidden="1">
+    <row r="182" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E182" t="s">
         <v>175</v>
       </c>
@@ -6072,7 +6187,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="183" spans="5:7" hidden="1">
+    <row r="183" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E183" t="s">
         <v>158</v>
       </c>
@@ -6083,7 +6198,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="184" spans="5:7" hidden="1">
+    <row r="184" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E184" t="s">
         <v>95</v>
       </c>
@@ -6094,7 +6209,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="185" spans="5:7" hidden="1">
+    <row r="185" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E185" t="s">
         <v>127</v>
       </c>
@@ -6105,7 +6220,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="186" spans="5:7" hidden="1">
+    <row r="186" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E186" t="s">
         <v>45</v>
       </c>
@@ -6116,7 +6231,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="187" spans="5:7" hidden="1">
+    <row r="187" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E187" t="s">
         <v>172</v>
       </c>
@@ -6127,7 +6242,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="188" spans="5:7" hidden="1">
+    <row r="188" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E188" t="s">
         <v>167</v>
       </c>
@@ -6138,7 +6253,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="189" spans="5:7" hidden="1">
+    <row r="189" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E189" t="s">
         <v>95</v>
       </c>
@@ -6149,7 +6264,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="190" spans="5:7" hidden="1">
+    <row r="190" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E190" t="s">
         <v>186</v>
       </c>
@@ -6160,7 +6275,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="191" spans="5:7" hidden="1">
+    <row r="191" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E191" t="s">
         <v>181</v>
       </c>
@@ -6171,7 +6286,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="192" spans="5:7" hidden="1">
+    <row r="192" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E192" t="s">
         <v>187</v>
       </c>
@@ -6182,7 +6297,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="193" spans="5:7" hidden="1">
+    <row r="193" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E193" t="s">
         <v>186</v>
       </c>
@@ -6193,7 +6308,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="194" spans="5:7">
+    <row r="194" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E194" t="s">
         <v>188</v>
       </c>
@@ -6204,7 +6319,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="195" spans="5:7" hidden="1">
+    <row r="195" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E195" t="s">
         <v>99</v>
       </c>
@@ -6215,7 +6330,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="196" spans="5:7" hidden="1">
+    <row r="196" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E196" t="s">
         <v>90</v>
       </c>
@@ -6226,7 +6341,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="197" spans="5:7" hidden="1">
+    <row r="197" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E197" t="s">
         <v>61</v>
       </c>
@@ -6237,7 +6352,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="198" spans="5:7" hidden="1">
+    <row r="198" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E198" t="s">
         <v>180</v>
       </c>
@@ -6248,7 +6363,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="199" spans="5:7" hidden="1">
+    <row r="199" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E199" t="s">
         <v>186</v>
       </c>
@@ -6259,7 +6374,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="200" spans="5:7" hidden="1">
+    <row r="200" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E200" t="s">
         <v>143</v>
       </c>
@@ -6270,7 +6385,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="201" spans="5:7" hidden="1">
+    <row r="201" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E201" t="s">
         <v>180</v>
       </c>
@@ -6281,7 +6396,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="202" spans="5:7" hidden="1">
+    <row r="202" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E202" t="s">
         <v>189</v>
       </c>
@@ -6292,7 +6407,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="203" spans="5:7" hidden="1">
+    <row r="203" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E203" t="s">
         <v>161</v>
       </c>
@@ -6303,7 +6418,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="204" spans="5:7" hidden="1">
+    <row r="204" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E204" t="s">
         <v>153</v>
       </c>
@@ -6314,7 +6429,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="205" spans="5:7">
+    <row r="205" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E205" t="s">
         <v>190</v>
       </c>
@@ -6325,7 +6440,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="206" spans="5:7" hidden="1">
+    <row r="206" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E206" s="1" t="s">
         <v>119</v>
       </c>
@@ -6336,7 +6451,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="207" spans="5:7" hidden="1">
+    <row r="207" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E207" t="s">
         <v>145</v>
       </c>
@@ -6347,7 +6462,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="208" spans="5:7" hidden="1">
+    <row r="208" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E208" t="s">
         <v>170</v>
       </c>
@@ -6358,7 +6473,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="209" spans="5:7" hidden="1">
+    <row r="209" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E209" t="s">
         <v>159</v>
       </c>
@@ -6369,7 +6484,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="210" spans="5:7" hidden="1">
+    <row r="210" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E210" s="1" t="s">
         <v>145</v>
       </c>
@@ -6380,7 +6495,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="211" spans="5:7" hidden="1">
+    <row r="211" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E211" s="1" t="s">
         <v>191</v>
       </c>
@@ -6391,7 +6506,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="212" spans="5:7" hidden="1">
+    <row r="212" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E212" t="s">
         <v>103</v>
       </c>
@@ -6402,7 +6517,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="213" spans="5:7" hidden="1">
+    <row r="213" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E213" s="1" t="s">
         <v>100</v>
       </c>
@@ -6413,7 +6528,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="214" spans="5:7" hidden="1">
+    <row r="214" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E214" t="s">
         <v>187</v>
       </c>
@@ -6424,7 +6539,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="215" spans="5:7" hidden="1">
+    <row r="215" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E215" t="s">
         <v>12</v>
       </c>
@@ -6435,7 +6550,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="216" spans="5:7" hidden="1">
+    <row r="216" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E216" t="s">
         <v>192</v>
       </c>
@@ -6446,7 +6561,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="217" spans="5:7">
+    <row r="217" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E217" t="s">
         <v>193</v>
       </c>
@@ -6457,7 +6572,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="218" spans="5:7" hidden="1">
+    <row r="218" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E218" t="s">
         <v>194</v>
       </c>
@@ -6468,7 +6583,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="219" spans="5:7" hidden="1">
+    <row r="219" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E219" t="s">
         <v>191</v>
       </c>
@@ -6479,7 +6594,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="220" spans="5:7" hidden="1">
+    <row r="220" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E220" t="s">
         <v>195</v>
       </c>
@@ -6490,7 +6605,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="221" spans="5:7" hidden="1">
+    <row r="221" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E221" t="s">
         <v>196</v>
       </c>
@@ -6501,7 +6616,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="222" spans="5:7" hidden="1">
+    <row r="222" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E222" t="s">
         <v>192</v>
       </c>
@@ -6512,7 +6627,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="223" spans="5:7" hidden="1">
+    <row r="223" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E223" s="1" t="s">
         <v>98</v>
       </c>
@@ -6523,7 +6638,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="224" spans="5:7" hidden="1">
+    <row r="224" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E224" t="s">
         <v>140</v>
       </c>
@@ -6534,7 +6649,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="225" spans="5:7" hidden="1">
+    <row r="225" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E225" t="s">
         <v>195</v>
       </c>
@@ -6545,7 +6660,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="226" spans="5:7" hidden="1">
+    <row r="226" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E226" s="1" t="s">
         <v>197</v>
       </c>
@@ -6556,7 +6671,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="227" spans="5:7" hidden="1">
+    <row r="227" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E227" t="s">
         <v>178</v>
       </c>
@@ -6567,7 +6682,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="228" spans="5:7" hidden="1">
+    <row r="228" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E228" s="1" t="s">
         <v>158</v>
       </c>
@@ -6578,7 +6693,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="229" spans="5:7" hidden="1">
+    <row r="229" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E229" t="s">
         <v>198</v>
       </c>
@@ -6589,7 +6704,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="230" spans="5:7" hidden="1">
+    <row r="230" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E230" t="s">
         <v>195</v>
       </c>
@@ -6600,7 +6715,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="231" spans="5:7" hidden="1">
+    <row r="231" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E231" t="s">
         <v>191</v>
       </c>
@@ -6611,7 +6726,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="232" spans="5:7" hidden="1">
+    <row r="232" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E232" t="s">
         <v>112</v>
       </c>
@@ -6622,7 +6737,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="233" spans="5:7" hidden="1">
+    <row r="233" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E233" t="s">
         <v>199</v>
       </c>
@@ -6633,7 +6748,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="234" spans="5:7" hidden="1">
+    <row r="234" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E234" t="s">
         <v>173</v>
       </c>
@@ -6644,7 +6759,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="235" spans="5:7" hidden="1">
+    <row r="235" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E235" t="s">
         <v>167</v>
       </c>
@@ -6655,7 +6770,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="236" spans="5:7" hidden="1">
+    <row r="236" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E236" s="1" t="s">
         <v>178</v>
       </c>
@@ -6666,7 +6781,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="237" spans="5:7" hidden="1">
+    <row r="237" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E237" t="s">
         <v>200</v>
       </c>
@@ -6677,7 +6792,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="238" spans="5:7" hidden="1">
+    <row r="238" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E238" t="s">
         <v>201</v>
       </c>
@@ -6688,7 +6803,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="239" spans="5:7" hidden="1">
+    <row r="239" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E239" t="s">
         <v>202</v>
       </c>
@@ -6699,7 +6814,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="240" spans="5:7" hidden="1">
+    <row r="240" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E240" t="s">
         <v>194</v>
       </c>
@@ -6710,7 +6825,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="241" spans="5:7" hidden="1">
+    <row r="241" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E241" t="s">
         <v>180</v>
       </c>
@@ -6721,7 +6836,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="242" spans="5:7" hidden="1">
+    <row r="242" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E242" s="1" t="s">
         <v>203</v>
       </c>
@@ -6732,7 +6847,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="243" spans="5:7" hidden="1">
+    <row r="243" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E243" t="s">
         <v>181</v>
       </c>
@@ -6743,7 +6858,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="244" spans="5:7" hidden="1">
+    <row r="244" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E244" t="s">
         <v>185</v>
       </c>
@@ -6754,7 +6869,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="245" spans="5:7" hidden="1">
+    <row r="245" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E245" s="1" t="s">
         <v>181</v>
       </c>
@@ -6765,7 +6880,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="246" spans="5:7" hidden="1">
+    <row r="246" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E246" s="1" t="s">
         <v>202</v>
       </c>
@@ -6776,7 +6891,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="247" spans="5:7" hidden="1">
+    <row r="247" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E247" t="s">
         <v>204</v>
       </c>
@@ -6787,7 +6902,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="248" spans="5:7" hidden="1">
+    <row r="248" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E248" t="s">
         <v>205</v>
       </c>
@@ -6798,7 +6913,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="249" spans="5:7" hidden="1">
+    <row r="249" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E249" t="s">
         <v>11</v>
       </c>
@@ -6809,7 +6924,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="250" spans="5:7" hidden="1">
+    <row r="250" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E250" t="s">
         <v>185</v>
       </c>
@@ -6820,7 +6935,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="251" spans="5:7">
+    <row r="251" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E251" t="s">
         <v>206</v>
       </c>
@@ -6831,7 +6946,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="252" spans="5:7" hidden="1">
+    <row r="252" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E252" t="s">
         <v>207</v>
       </c>
@@ -6842,7 +6957,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="253" spans="5:7" hidden="1">
+    <row r="253" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E253" s="1" t="s">
         <v>45</v>
       </c>
@@ -6853,7 +6968,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="254" spans="5:7" hidden="1">
+    <row r="254" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E254" t="s">
         <v>181</v>
       </c>
@@ -6864,7 +6979,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="255" spans="5:7" hidden="1">
+    <row r="255" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E255" t="s">
         <v>187</v>
       </c>
@@ -6875,7 +6990,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="256" spans="5:7" hidden="1">
+    <row r="256" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E256" t="s">
         <v>208</v>
       </c>
@@ -6886,7 +7001,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="257" spans="5:7" hidden="1">
+    <row r="257" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E257" s="1" t="s">
         <v>182</v>
       </c>
@@ -6897,7 +7012,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="258" spans="5:7" hidden="1">
+    <row r="258" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E258" t="s">
         <v>206</v>
       </c>
@@ -6908,7 +7023,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="259" spans="5:7" hidden="1">
+    <row r="259" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E259" t="s">
         <v>209</v>
       </c>
@@ -6919,7 +7034,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="260" spans="5:7" hidden="1">
+    <row r="260" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E260" t="s">
         <v>192</v>
       </c>
@@ -6930,7 +7045,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="261" spans="5:7" hidden="1">
+    <row r="261" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E261" t="s">
         <v>205</v>
       </c>
@@ -6941,7 +7056,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="262" spans="5:7" hidden="1">
+    <row r="262" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E262" t="s">
         <v>205</v>
       </c>
@@ -6952,7 +7067,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="263" spans="5:7" hidden="1">
+    <row r="263" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E263" t="s">
         <v>210</v>
       </c>
@@ -6963,7 +7078,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="264" spans="5:7" hidden="1">
+    <row r="264" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E264" t="s">
         <v>16</v>
       </c>
@@ -6974,7 +7089,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="265" spans="5:7" hidden="1">
+    <row r="265" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E265" t="s">
         <v>199</v>
       </c>
@@ -6985,7 +7100,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="266" spans="5:7" hidden="1">
+    <row r="266" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E266" t="s">
         <v>14</v>
       </c>
@@ -6996,7 +7111,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="267" spans="5:7" hidden="1">
+    <row r="267" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E267" t="s">
         <v>166</v>
       </c>
@@ -7007,7 +7122,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="268" spans="5:7" hidden="1">
+    <row r="268" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E268" s="1" t="s">
         <v>210</v>
       </c>
@@ -7018,7 +7133,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="269" spans="5:7" hidden="1">
+    <row r="269" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E269" t="s">
         <v>206</v>
       </c>
@@ -7029,7 +7144,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="270" spans="5:7" hidden="1">
+    <row r="270" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E270" t="s">
         <v>210</v>
       </c>
@@ -7040,7 +7155,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="271" spans="5:7" hidden="1">
+    <row r="271" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E271" t="s">
         <v>211</v>
       </c>
@@ -7051,7 +7166,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="272" spans="5:7" hidden="1">
+    <row r="272" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E272" t="s">
         <v>212</v>
       </c>
@@ -7062,7 +7177,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="273" spans="5:7" hidden="1">
+    <row r="273" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E273" t="s">
         <v>213</v>
       </c>
@@ -7073,7 +7188,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="274" spans="5:7" hidden="1">
+    <row r="274" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E274" s="1" t="s">
         <v>199</v>
       </c>
@@ -7084,7 +7199,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="275" spans="5:7" hidden="1">
+    <row r="275" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E275" t="s">
         <v>199</v>
       </c>
@@ -7095,7 +7210,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="276" spans="5:7" hidden="1">
+    <row r="276" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E276" t="s">
         <v>205</v>
       </c>
@@ -7106,7 +7221,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="277" spans="5:7" hidden="1">
+    <row r="277" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E277" t="s">
         <v>214</v>
       </c>
@@ -7117,7 +7232,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="278" spans="5:7" hidden="1">
+    <row r="278" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E278" s="1" t="s">
         <v>192</v>
       </c>
@@ -7128,7 +7243,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="279" spans="5:7" hidden="1">
+    <row r="279" spans="5:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="E279" t="s">
         <v>200</v>
       </c>
@@ -7152,18 +7267,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F3D4C80-4545-4A65-8AF3-1F279FF51CAB}">
   <dimension ref="A1:W98"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="14.45">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7219,7 +7334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="14.45">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -7275,7 +7390,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="14.45">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>62</v>
       </c>
@@ -7331,7 +7446,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="14.45">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -7387,7 +7502,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="14.45">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -7443,7 +7558,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="14.45">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -7499,7 +7614,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="14.45">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7555,7 +7670,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="14.45">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -7611,7 +7726,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="14.45">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -7667,7 +7782,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="14.45">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>138</v>
       </c>
@@ -7723,7 +7838,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="14.45">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="E11" s="1" t="s">
         <v>71</v>
       </c>
@@ -7770,7 +7885,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="14.45">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
         <v>111</v>
       </c>
@@ -7817,7 +7932,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="14.45">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="E13" s="2" t="s">
         <v>124</v>
       </c>
@@ -7864,7 +7979,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="14.45">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="E14" t="s">
         <v>46</v>
       </c>
@@ -7911,7 +8026,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="14.45">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="E15" t="s">
         <v>6</v>
       </c>
@@ -7958,7 +8073,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="14.45">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="E16" t="s">
         <v>152</v>
       </c>
@@ -8005,7 +8120,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="17" spans="5:23" ht="14.45">
+    <row r="17" spans="5:23" x14ac:dyDescent="0.2">
       <c r="E17" t="s">
         <v>160</v>
       </c>
@@ -8052,7 +8167,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="18" spans="5:23" ht="14.45">
+    <row r="18" spans="5:23" x14ac:dyDescent="0.2">
       <c r="E18" t="s">
         <v>136</v>
       </c>
@@ -8099,7 +8214,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="19" spans="5:23" ht="14.45">
+    <row r="19" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I19" s="1" t="s">
         <v>72</v>
       </c>
@@ -8137,7 +8252,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="5:23" ht="14.45">
+    <row r="20" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I20" t="s">
         <v>76</v>
       </c>
@@ -8175,7 +8290,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="21" spans="5:23" ht="14.45">
+    <row r="21" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I21" t="s">
         <v>84</v>
       </c>
@@ -8213,7 +8328,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="22" spans="5:23" ht="14.45">
+    <row r="22" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I22" t="s">
         <v>96</v>
       </c>
@@ -8251,7 +8366,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="23" spans="5:23" ht="14.45">
+    <row r="23" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I23" t="s">
         <v>74</v>
       </c>
@@ -8289,7 +8404,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="24" spans="5:23" ht="14.45">
+    <row r="24" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I24" t="s">
         <v>64</v>
       </c>
@@ -8327,7 +8442,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="25" spans="5:23" ht="14.45">
+    <row r="25" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I25" t="s">
         <v>84</v>
       </c>
@@ -8365,7 +8480,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="26" spans="5:23" ht="14.45">
+    <row r="26" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I26" t="s">
         <v>66</v>
       </c>
@@ -8403,7 +8518,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="27" spans="5:23" ht="14.45">
+    <row r="27" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I27" t="s">
         <v>94</v>
       </c>
@@ -8432,7 +8547,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="28" spans="5:23" ht="14.45">
+    <row r="28" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I28" t="s">
         <v>105</v>
       </c>
@@ -8461,7 +8576,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="29" spans="5:23" ht="14.45">
+    <row r="29" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I29" t="s">
         <v>66</v>
       </c>
@@ -8490,7 +8605,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="30" spans="5:23" ht="14.45">
+    <row r="30" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I30" t="s">
         <v>111</v>
       </c>
@@ -8519,7 +8634,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="31" spans="5:23" ht="14.45">
+    <row r="31" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I31" t="s">
         <v>120</v>
       </c>
@@ -8548,7 +8663,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="32" spans="5:23" ht="14.45">
+    <row r="32" spans="5:23" x14ac:dyDescent="0.2">
       <c r="I32" t="s">
         <v>129</v>
       </c>
@@ -8577,7 +8692,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="33" spans="9:23" ht="14.45">
+    <row r="33" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I33" t="s">
         <v>125</v>
       </c>
@@ -8606,7 +8721,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="34" spans="9:23" ht="14.45">
+    <row r="34" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I34" t="s">
         <v>117</v>
       </c>
@@ -8635,7 +8750,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="35" spans="9:23" ht="14.45">
+    <row r="35" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I35" t="s">
         <v>122</v>
       </c>
@@ -8664,7 +8779,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="36" spans="9:23" ht="14.45">
+    <row r="36" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I36" t="s">
         <v>132</v>
       </c>
@@ -8693,7 +8808,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="37" spans="9:23" ht="14.45">
+    <row r="37" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I37" t="s">
         <v>126</v>
       </c>
@@ -8722,7 +8837,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="38" spans="9:23" ht="14.45">
+    <row r="38" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I38" t="s">
         <v>117</v>
       </c>
@@ -8751,7 +8866,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="9:23" ht="14.45">
+    <row r="39" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I39" t="s">
         <v>120</v>
       </c>
@@ -8780,7 +8895,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="40" spans="9:23" ht="14.45">
+    <row r="40" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I40" t="s">
         <v>136</v>
       </c>
@@ -8809,7 +8924,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="41" spans="9:23" ht="14.45">
+    <row r="41" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I41" t="s">
         <v>80</v>
       </c>
@@ -8838,7 +8953,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="42" spans="9:23" ht="14.45">
+    <row r="42" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I42" t="s">
         <v>107</v>
       </c>
@@ -8867,7 +8982,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="43" spans="9:23" ht="14.45">
+    <row r="43" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I43" t="s">
         <v>139</v>
       </c>
@@ -8896,7 +9011,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="44" spans="9:23" ht="14.45">
+    <row r="44" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I44" t="s">
         <v>72</v>
       </c>
@@ -8925,7 +9040,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="45" spans="9:23" ht="14.45">
+    <row r="45" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I45" t="s">
         <v>132</v>
       </c>
@@ -8954,7 +9069,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="46" spans="9:23" ht="14.45">
+    <row r="46" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I46" s="1" t="s">
         <v>117</v>
       </c>
@@ -8983,7 +9098,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="47" spans="9:23" ht="14.45">
+    <row r="47" spans="9:23" x14ac:dyDescent="0.2">
       <c r="I47" t="s">
         <v>136</v>
       </c>
@@ -9012,7 +9127,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="48" spans="9:23" ht="14.45">
+    <row r="48" spans="9:23" x14ac:dyDescent="0.2">
       <c r="Q48" t="s">
         <v>194</v>
       </c>
@@ -9032,7 +9147,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="49" spans="17:23" ht="14.45">
+    <row r="49" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q49" t="s">
         <v>200</v>
       </c>
@@ -9052,7 +9167,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="50" spans="17:23" ht="14.45">
+    <row r="50" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q50" t="s">
         <v>215</v>
       </c>
@@ -9072,7 +9187,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="51" spans="17:23" ht="14.45">
+    <row r="51" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q51" s="1" t="s">
         <v>185</v>
       </c>
@@ -9092,7 +9207,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="52" spans="17:23" ht="14.45">
+    <row r="52" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q52" t="s">
         <v>192</v>
       </c>
@@ -9112,7 +9227,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="53" spans="17:23" ht="14.45">
+    <row r="53" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q53" t="s">
         <v>206</v>
       </c>
@@ -9132,7 +9247,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="54" spans="17:23" ht="14.45">
+    <row r="54" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q54" t="s">
         <v>180</v>
       </c>
@@ -9152,7 +9267,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="55" spans="17:23" ht="14.45">
+    <row r="55" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q55" t="s">
         <v>187</v>
       </c>
@@ -9172,7 +9287,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="56" spans="17:23" ht="14.45">
+    <row r="56" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q56" t="s">
         <v>205</v>
       </c>
@@ -9192,7 +9307,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="57" spans="17:23" ht="14.45">
+    <row r="57" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q57" t="s">
         <v>211</v>
       </c>
@@ -9212,7 +9327,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="58" spans="17:23" ht="14.45">
+    <row r="58" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q58" t="s">
         <v>210</v>
       </c>
@@ -9232,7 +9347,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="59" spans="17:23" ht="14.45">
+    <row r="59" spans="17:23" x14ac:dyDescent="0.2">
       <c r="Q59" t="s">
         <v>214</v>
       </c>
@@ -9252,7 +9367,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="60" spans="17:23" ht="14.45">
+    <row r="60" spans="17:23" x14ac:dyDescent="0.2">
       <c r="U60" t="s">
         <v>119</v>
       </c>
@@ -9263,7 +9378,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="61" spans="17:23" ht="14.45">
+    <row r="61" spans="17:23" x14ac:dyDescent="0.2">
       <c r="U61" s="1" t="s">
         <v>153</v>
       </c>
@@ -9274,7 +9389,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="62" spans="17:23" ht="14.45">
+    <row r="62" spans="17:23" x14ac:dyDescent="0.2">
       <c r="U62" t="s">
         <v>42</v>
       </c>
@@ -9285,7 +9400,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="63" spans="17:23" ht="14.45">
+    <row r="63" spans="17:23" x14ac:dyDescent="0.2">
       <c r="U63" t="s">
         <v>131</v>
       </c>
@@ -9296,7 +9411,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="64" spans="17:23" ht="14.45">
+    <row r="64" spans="17:23" x14ac:dyDescent="0.2">
       <c r="U64" t="s">
         <v>128</v>
       </c>
@@ -9307,7 +9422,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="65" spans="21:23" ht="14.45">
+    <row r="65" spans="21:23" x14ac:dyDescent="0.2">
       <c r="U65" t="s">
         <v>106</v>
       </c>
@@ -9318,7 +9433,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="66" spans="21:23" ht="14.45">
+    <row r="66" spans="21:23" x14ac:dyDescent="0.2">
       <c r="U66" t="s">
         <v>183</v>
       </c>
@@ -9329,7 +9444,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="67" spans="21:23" ht="14.45">
+    <row r="67" spans="21:23" x14ac:dyDescent="0.2">
       <c r="U67" t="s">
         <v>186</v>
       </c>
@@ -9340,7 +9455,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="68" spans="21:23" ht="14.45">
+    <row r="68" spans="21:23" x14ac:dyDescent="0.2">
       <c r="U68" t="s">
         <v>134</v>
       </c>
@@ -9351,7 +9466,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="69" spans="21:23" ht="14.45">
+    <row r="69" spans="21:23" x14ac:dyDescent="0.2">
       <c r="U69" t="s">
         <v>170</v>
       </c>
@@ -9362,7 +9477,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="70" spans="21:23" ht="15" customHeight="1">
+    <row r="70" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U70" t="s">
         <v>143</v>
       </c>
@@ -9373,7 +9488,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="71" spans="21:23" ht="15" customHeight="1">
+    <row r="71" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U71" t="s">
         <v>140</v>
       </c>
@@ -9384,7 +9499,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="72" spans="21:23" ht="15" customHeight="1">
+    <row r="72" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U72" t="s">
         <v>90</v>
       </c>
@@ -9395,7 +9510,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="73" spans="21:23" ht="15" customHeight="1">
+    <row r="73" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U73" t="s">
         <v>95</v>
       </c>
@@ -9406,7 +9521,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="74" spans="21:23" ht="15" customHeight="1">
+    <row r="74" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U74" t="s">
         <v>134</v>
       </c>
@@ -9417,7 +9532,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="75" spans="21:23" ht="15" customHeight="1">
+    <row r="75" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U75" t="s">
         <v>140</v>
       </c>
@@ -9428,7 +9543,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="76" spans="21:23" ht="15" customHeight="1">
+    <row r="76" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U76" t="s">
         <v>153</v>
       </c>
@@ -9439,7 +9554,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="77" spans="21:23" ht="15" customHeight="1">
+    <row r="77" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U77" t="s">
         <v>100</v>
       </c>
@@ -9450,7 +9565,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="78" spans="21:23" ht="15" customHeight="1">
+    <row r="78" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U78" t="s">
         <v>42</v>
       </c>
@@ -9461,7 +9576,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="79" spans="21:23" ht="15" customHeight="1">
+    <row r="79" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U79" t="s">
         <v>102</v>
       </c>
@@ -9472,7 +9587,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="80" spans="21:23" ht="15" customHeight="1">
+    <row r="80" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U80" t="s">
         <v>123</v>
       </c>
@@ -9483,7 +9598,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="81" spans="21:23" ht="15" customHeight="1">
+    <row r="81" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U81" t="s">
         <v>187</v>
       </c>
@@ -9494,7 +9609,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="82" spans="21:23" ht="15" customHeight="1">
+    <row r="82" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U82" t="s">
         <v>159</v>
       </c>
@@ -9505,7 +9620,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="83" spans="21:23" ht="15" customHeight="1">
+    <row r="83" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U83" t="s">
         <v>133</v>
       </c>
@@ -9516,7 +9631,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="84" spans="21:23" ht="15" customHeight="1">
+    <row r="84" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U84" t="s">
         <v>175</v>
       </c>
@@ -9527,7 +9642,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="85" spans="21:23" ht="15" customHeight="1">
+    <row r="85" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U85" t="s">
         <v>193</v>
       </c>
@@ -9538,7 +9653,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="86" spans="21:23" ht="15" customHeight="1">
+    <row r="86" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U86" t="s">
         <v>166</v>
       </c>
@@ -9549,7 +9664,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="87" spans="21:23" ht="15" customHeight="1">
+    <row r="87" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U87" t="s">
         <v>191</v>
       </c>
@@ -9560,7 +9675,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="88" spans="21:23" ht="15" customHeight="1">
+    <row r="88" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U88" t="s">
         <v>175</v>
       </c>
@@ -9571,7 +9686,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="89" spans="21:23" ht="15" customHeight="1">
+    <row r="89" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U89" t="s">
         <v>186</v>
       </c>
@@ -9582,7 +9697,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="90" spans="21:23" ht="15" customHeight="1">
+    <row r="90" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U90" t="s">
         <v>99</v>
       </c>
@@ -9593,7 +9708,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="91" spans="21:23" ht="15" customHeight="1">
+    <row r="91" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U91" t="s">
         <v>196</v>
       </c>
@@ -9604,7 +9719,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="92" spans="21:23" ht="15" customHeight="1">
+    <row r="92" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U92" t="s">
         <v>198</v>
       </c>
@@ -9615,7 +9730,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="93" spans="21:23" ht="15" customHeight="1">
+    <row r="93" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U93" t="s">
         <v>207</v>
       </c>
@@ -9626,7 +9741,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="94" spans="21:23" ht="15" customHeight="1">
+    <row r="94" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U94" t="s">
         <v>213</v>
       </c>
@@ -9637,7 +9752,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="95" spans="21:23" ht="15" customHeight="1">
+    <row r="95" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U95" t="s">
         <v>206</v>
       </c>
@@ -9648,7 +9763,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="96" spans="21:23" ht="15" customHeight="1">
+    <row r="96" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U96" t="s">
         <v>206</v>
       </c>
@@ -9659,7 +9774,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="97" spans="21:23" ht="15" customHeight="1">
+    <row r="97" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U97" t="s">
         <v>209</v>
       </c>
@@ -9670,7 +9785,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="98" spans="21:23" ht="15" customHeight="1">
+    <row r="98" spans="21:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="U98" t="s">
         <v>166</v>
       </c>
@@ -9697,16 +9812,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D1EC75F-67B5-498A-B0E3-7E8F00E5C4DB}">
   <dimension ref="A1:K99"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9717,10 +9832,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>248</v>
+      </c>
+      <c r="E1" t="s">
         <v>216</v>
-      </c>
-      <c r="E1" t="s">
-        <v>217</v>
       </c>
       <c r="G1" t="s">
         <v>0</v>
@@ -9732,13 +9847,13 @@
         <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9752,7 +9867,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="H2" s="3">
         <v>3.1789351851851848E-3</v>
@@ -9764,7 +9879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -9790,7 +9905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>69</v>
       </c>
@@ -9816,7 +9931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>168</v>
       </c>
@@ -9842,7 +9957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -9868,7 +9983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>65</v>
       </c>
@@ -9894,7 +10009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -9908,7 +10023,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="H8" s="3">
         <v>3.3651620370370372E-3</v>
@@ -9920,7 +10035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -9946,7 +10061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -9957,7 +10072,7 @@
         <v>2025</v>
       </c>
       <c r="G10" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="H10" s="3">
         <v>3.3694444444444444E-3</v>
@@ -9969,7 +10084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -9995,7 +10110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -10021,9 +10136,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="B13" s="3">
         <v>2.7901620370370367E-3</v>
@@ -10044,7 +10159,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>175</v>
       </c>
@@ -10067,7 +10182,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -10081,7 +10196,7 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="H15" s="3">
         <v>3.4459490740740744E-3</v>
@@ -10093,7 +10208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -10116,7 +10231,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -10139,7 +10254,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -10153,7 +10268,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H18" s="3">
         <v>3.4886574074074078E-3</v>
@@ -10165,7 +10280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -10185,7 +10300,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -10205,7 +10320,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -10228,7 +10343,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -10239,7 +10354,7 @@
         <v>2024</v>
       </c>
       <c r="E22" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G22" t="s">
         <v>87</v>
@@ -10254,7 +10369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>173</v>
       </c>
@@ -10268,7 +10383,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="H23" s="3">
         <v>3.5362268518518516E-3</v>
@@ -10277,7 +10392,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -10297,7 +10412,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>170</v>
       </c>
@@ -10308,7 +10423,7 @@
         <v>2024</v>
       </c>
       <c r="E25" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G25" t="s">
         <v>6</v>
@@ -10323,7 +10438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>171</v>
       </c>
@@ -10346,10 +10461,10 @@
         <v>2024</v>
       </c>
       <c r="J26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>168</v>
       </c>
@@ -10360,7 +10475,7 @@
         <v>2025</v>
       </c>
       <c r="G27" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="H27" s="3">
         <v>3.5533564814814816E-3</v>
@@ -10369,7 +10484,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -10389,7 +10504,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>103</v>
       </c>
@@ -10412,7 +10527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>99</v>
       </c>
@@ -10423,7 +10538,7 @@
         <v>2024</v>
       </c>
       <c r="E30" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G30" t="s">
         <v>66</v>
@@ -10435,10 +10550,10 @@
         <v>2024</v>
       </c>
       <c r="J30" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -10458,7 +10573,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>169</v>
       </c>
@@ -10481,7 +10596,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -10492,7 +10607,7 @@
         <v>2024</v>
       </c>
       <c r="E33" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G33" t="s">
         <v>84</v>
@@ -10504,7 +10619,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -10524,10 +10639,10 @@
         <v>2024</v>
       </c>
       <c r="J34" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>103</v>
       </c>
@@ -10538,7 +10653,7 @@
         <v>2024</v>
       </c>
       <c r="E35" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G35" t="s">
         <v>105</v>
@@ -10553,7 +10668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>99</v>
       </c>
@@ -10564,7 +10679,7 @@
         <v>2025</v>
       </c>
       <c r="G36" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H36" s="3">
         <v>3.7090277777777781E-3</v>
@@ -10573,10 +10688,10 @@
         <v>2024</v>
       </c>
       <c r="J36" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -10596,7 +10711,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>147</v>
       </c>
@@ -10619,7 +10734,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -10642,7 +10757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>106</v>
       </c>
@@ -10662,10 +10777,10 @@
         <v>2024</v>
       </c>
       <c r="J40" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -10676,7 +10791,7 @@
         <v>2025</v>
       </c>
       <c r="G41" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="H41" s="3">
         <v>3.780902777777778E-3</v>
@@ -10685,7 +10800,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>88</v>
       </c>
@@ -10708,7 +10823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -10719,7 +10834,7 @@
         <v>2024</v>
       </c>
       <c r="E43" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G43" t="s">
         <v>84</v>
@@ -10731,10 +10846,10 @@
         <v>2024</v>
       </c>
       <c r="J43" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>167</v>
       </c>
@@ -10754,7 +10869,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -10765,7 +10880,7 @@
         <v>2025</v>
       </c>
       <c r="G45" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H45" s="3">
         <v>3.8690972222222226E-3</v>
@@ -10774,7 +10889,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>127</v>
       </c>
@@ -10794,7 +10909,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -10817,10 +10932,10 @@
         <v>2024</v>
       </c>
       <c r="J47" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -10840,7 +10955,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>102</v>
       </c>
@@ -10851,7 +10966,7 @@
         <v>2024</v>
       </c>
       <c r="E49" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G49" t="s">
         <v>138</v>
@@ -10863,7 +10978,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -10883,7 +10998,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>35</v>
       </c>
@@ -10906,7 +11021,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>88</v>
       </c>
@@ -10917,7 +11032,7 @@
         <v>2024</v>
       </c>
       <c r="E52" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G52" t="s">
         <v>132</v>
@@ -10929,7 +11044,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>185</v>
       </c>
@@ -10952,9 +11067,9 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B54" s="3">
         <v>2.9327546296296293E-3</v>
@@ -10972,7 +11087,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>186</v>
       </c>
@@ -10992,7 +11107,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>153</v>
       </c>
@@ -11003,7 +11118,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>140</v>
       </c>
@@ -11014,10 +11129,10 @@
         <v>2024</v>
       </c>
       <c r="E57" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -11028,10 +11143,10 @@
         <v>2024</v>
       </c>
       <c r="E58" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>81</v>
       </c>
@@ -11042,7 +11157,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>143</v>
       </c>
@@ -11053,10 +11168,10 @@
         <v>2024</v>
       </c>
       <c r="E60" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>167</v>
       </c>
@@ -11067,7 +11182,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -11081,7 +11196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>173</v>
       </c>
@@ -11092,7 +11207,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>187</v>
       </c>
@@ -11103,10 +11218,10 @@
         <v>2024</v>
       </c>
       <c r="E64" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>143</v>
       </c>
@@ -11117,7 +11232,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -11128,10 +11243,10 @@
         <v>2024</v>
       </c>
       <c r="E66" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>175</v>
       </c>
@@ -11142,7 +11257,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>166</v>
       </c>
@@ -11153,10 +11268,10 @@
         <v>2024</v>
       </c>
       <c r="E68" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -11167,7 +11282,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>159</v>
       </c>
@@ -11178,7 +11293,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>153</v>
       </c>
@@ -11189,7 +11304,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -11203,7 +11318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>145</v>
       </c>
@@ -11214,10 +11329,10 @@
         <v>2024</v>
       </c>
       <c r="E73" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -11231,7 +11346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>186</v>
       </c>
@@ -11242,7 +11357,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>133</v>
       </c>
@@ -11256,7 +11371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>123</v>
       </c>
@@ -11267,7 +11382,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>192</v>
       </c>
@@ -11278,7 +11393,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>95</v>
       </c>
@@ -11289,10 +11404,10 @@
         <v>2024</v>
       </c>
       <c r="E79" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>166</v>
       </c>
@@ -11303,7 +11418,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>193</v>
       </c>
@@ -11317,9 +11432,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B82" s="3">
         <v>3.0601851851851849E-3</v>
@@ -11328,7 +11443,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>209</v>
       </c>
@@ -11342,7 +11457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>196</v>
       </c>
@@ -11353,7 +11468,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>185</v>
       </c>
@@ -11364,10 +11479,10 @@
         <v>2024</v>
       </c>
       <c r="E85" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>208</v>
       </c>
@@ -11378,10 +11493,10 @@
         <v>2024</v>
       </c>
       <c r="E86" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>185</v>
       </c>
@@ -11392,7 +11507,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -11403,7 +11518,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>211</v>
       </c>
@@ -11414,10 +11529,10 @@
         <v>2024</v>
       </c>
       <c r="E89" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>188</v>
       </c>
@@ -11428,7 +11543,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>205</v>
       </c>
@@ -11439,7 +11554,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>205</v>
       </c>
@@ -11450,7 +11565,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>16</v>
       </c>
@@ -11464,7 +11579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -11475,7 +11590,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -11486,7 +11601,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>206</v>
       </c>
@@ -11497,7 +11612,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>206</v>
       </c>
@@ -11508,10 +11623,10 @@
         <v>2024</v>
       </c>
       <c r="E97" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>206</v>
       </c>
@@ -11525,9 +11640,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B99" s="3">
         <v>3.4574074074074077E-3</v>
@@ -11548,16 +11663,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2265977-8617-49BB-9F30-EABEA05BC0E5}">
   <dimension ref="A1:AA51"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -11577,16 +11692,16 @@
         <v>2</v>
       </c>
       <c r="H1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="I1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="J1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="K1" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="M1" t="s">
         <v>0</v>
@@ -11598,19 +11713,19 @@
         <v>2</v>
       </c>
       <c r="P1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Q1" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="R1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="S1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="T1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="V1" s="10" t="s">
         <v>0</v>
@@ -11622,16 +11737,16 @@
         <v>2</v>
       </c>
       <c r="Y1" s="10" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="Z1" s="10" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AA1" s="10" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -11691,7 +11806,7 @@
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -11759,7 +11874,7 @@
       <c r="Z3" s="5"/>
       <c r="AA3" s="5"/>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -11827,7 +11942,7 @@
       <c r="Z4" s="5"/>
       <c r="AA4" s="5"/>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>55</v>
       </c>
@@ -11895,7 +12010,7 @@
       <c r="Z5" s="5"/>
       <c r="AA5" s="5"/>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>167</v>
       </c>
@@ -11963,7 +12078,7 @@
       <c r="Z6" s="5"/>
       <c r="AA6" s="5"/>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>173</v>
       </c>
@@ -11974,7 +12089,7 @@
         <v>2025</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="F7" s="5">
         <v>3.3993055555555556E-3</v>
@@ -12029,7 +12144,7 @@
         <v>2.244097222222222E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>127</v>
       </c>
@@ -12095,7 +12210,7 @@
         <v>2.7453703703703702E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
@@ -12163,7 +12278,7 @@
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>193</v>
       </c>
@@ -12174,7 +12289,7 @@
         <v>2026</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="F10" s="5">
         <v>3.4612268518518521E-3</v>
@@ -12211,7 +12326,7 @@
         <v>2.7263888888888889E-3</v>
       </c>
       <c r="V10" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="W10" s="5">
         <v>8.1122685185185187E-3</v>
@@ -12223,7 +12338,7 @@
       <c r="Z10" s="5"/>
       <c r="AA10" s="5"/>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>35</v>
       </c>
@@ -12255,7 +12370,7 @@
         <v>9.0439814814814821E-4</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N11" s="5">
         <v>1.3338541666666667E-2</v>
@@ -12297,7 +12412,7 @@
         <v>2.8336805555555559E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
@@ -12365,7 +12480,7 @@
       <c r="Z12" s="5"/>
       <c r="AA12" s="5"/>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>151</v>
       </c>
@@ -12425,7 +12540,7 @@
       <c r="Z13" s="5"/>
       <c r="AA13" s="5"/>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>196</v>
       </c>
@@ -12457,7 +12572,7 @@
         <v>9.3807870370370367E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>116</v>
       </c>
@@ -12489,7 +12604,7 @@
         <v>9.7615740740740746E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>175</v>
       </c>
@@ -12521,7 +12636,7 @@
         <v>9.3969907407407403E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>123</v>
       </c>
@@ -12553,7 +12668,7 @@
         <v>9.4189814814814809E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>153</v>
       </c>
@@ -12583,7 +12698,7 @@
         <v>1.009027777777778E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>183</v>
       </c>
@@ -12594,7 +12709,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>187</v>
       </c>
@@ -12605,7 +12720,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>88</v>
       </c>
@@ -12616,7 +12731,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>47</v>
       </c>
@@ -12627,7 +12742,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>185</v>
       </c>
@@ -12638,7 +12753,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>153</v>
       </c>
@@ -12649,7 +12764,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>16</v>
       </c>
@@ -12660,7 +12775,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>192</v>
       </c>
@@ -12671,7 +12786,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>185</v>
       </c>
@@ -12682,7 +12797,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>39</v>
       </c>
@@ -12693,7 +12808,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>102</v>
       </c>
@@ -12704,7 +12819,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>185</v>
       </c>
@@ -12715,7 +12830,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>143</v>
       </c>
@@ -12726,7 +12841,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>31</v>
       </c>
@@ -12737,7 +12852,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>205</v>
       </c>
@@ -12748,7 +12863,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>14</v>
       </c>
@@ -12759,7 +12874,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>134</v>
       </c>
@@ -12770,7 +12885,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>211</v>
       </c>
@@ -12781,7 +12896,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>206</v>
       </c>
@@ -12792,7 +12907,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>206</v>
       </c>
@@ -12803,7 +12918,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>6</v>
       </c>
@@ -12814,7 +12929,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>6</v>
       </c>
@@ -12825,7 +12940,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>60</v>
       </c>
@@ -12836,7 +12951,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>87</v>
       </c>
@@ -12847,9 +12962,9 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B43" s="5">
         <v>1.7869212962962962E-3</v>
@@ -12858,7 +12973,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>72</v>
       </c>
@@ -12869,7 +12984,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>111</v>
       </c>
@@ -12880,7 +12995,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>117</v>
       </c>
@@ -12891,7 +13006,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>132</v>
       </c>
@@ -12902,7 +13017,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>132</v>
       </c>
@@ -12913,7 +13028,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>132</v>
       </c>
@@ -12924,7 +13039,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>84</v>
       </c>
@@ -12935,7 +13050,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>80</v>
       </c>
@@ -12960,14 +13075,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{337791DD-2F30-41DE-AFA8-014D8942629C}">
   <dimension ref="A1:H151"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12978,7 +13093,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>0</v>
@@ -12990,7 +13105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>103</v>
       </c>
@@ -13001,7 +13116,7 @@
         <v>2025</v>
       </c>
       <c r="D2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>12</v>
@@ -13013,7 +13128,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>127</v>
       </c>
@@ -13024,7 +13139,7 @@
         <v>2025</v>
       </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>35</v>
@@ -13036,7 +13151,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>170</v>
       </c>
@@ -13047,7 +13162,7 @@
         <v>2024</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>81</v>
@@ -13059,7 +13174,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>175</v>
       </c>
@@ -13070,7 +13185,7 @@
         <v>2026</v>
       </c>
       <c r="D5" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>143</v>
@@ -13082,7 +13197,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>110</v>
       </c>
@@ -13093,7 +13208,7 @@
         <v>2021</v>
       </c>
       <c r="D6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>11</v>
@@ -13105,7 +13220,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>29</v>
       </c>
@@ -13116,7 +13231,7 @@
         <v>2025</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>81</v>
@@ -13128,7 +13243,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>131</v>
       </c>
@@ -13139,7 +13254,7 @@
         <v>2021</v>
       </c>
       <c r="D8" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>188</v>
@@ -13151,7 +13266,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>127</v>
       </c>
@@ -13162,7 +13277,7 @@
         <v>2024</v>
       </c>
       <c r="D9" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>16</v>
@@ -13174,7 +13289,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>77</v>
       </c>
@@ -13185,10 +13300,10 @@
         <v>2026</v>
       </c>
       <c r="D10" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="G10" s="14">
         <v>3.4879629629629631E-3</v>
@@ -13197,7 +13312,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>55</v>
       </c>
@@ -13208,7 +13323,7 @@
         <v>2026</v>
       </c>
       <c r="D11" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>26</v>
@@ -13220,7 +13335,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>99</v>
       </c>
@@ -13231,10 +13346,10 @@
         <v>2025</v>
       </c>
       <c r="D12" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="G12" s="14">
         <v>3.6872685185185185E-3</v>
@@ -13243,7 +13358,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>116</v>
       </c>
@@ -13254,7 +13369,7 @@
         <v>2024</v>
       </c>
       <c r="D13" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>64</v>
@@ -13266,7 +13381,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>88</v>
       </c>
@@ -13277,10 +13392,10 @@
         <v>2025</v>
       </c>
       <c r="D14" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="G14" s="14">
         <v>3.7975694444444446E-3</v>
@@ -13289,7 +13404,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>175</v>
       </c>
@@ -13300,7 +13415,7 @@
         <v>2025</v>
       </c>
       <c r="D15" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>52</v>
@@ -13312,7 +13427,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>35</v>
       </c>
@@ -13323,7 +13438,7 @@
         <v>2026</v>
       </c>
       <c r="D16" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>85</v>
@@ -13335,7 +13450,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>183</v>
       </c>
@@ -13346,7 +13461,7 @@
         <v>2026</v>
       </c>
       <c r="D17" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>87</v>
@@ -13358,7 +13473,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>25</v>
       </c>
@@ -13369,7 +13484,7 @@
         <v>2024</v>
       </c>
       <c r="D18" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>84</v>
@@ -13381,7 +13496,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>183</v>
       </c>
@@ -13392,7 +13507,7 @@
         <v>2025</v>
       </c>
       <c r="D19" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>76</v>
@@ -13404,7 +13519,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>131</v>
       </c>
@@ -13415,7 +13530,7 @@
         <v>2023</v>
       </c>
       <c r="D20" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>96</v>
@@ -13427,7 +13542,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>103</v>
       </c>
@@ -13438,7 +13553,7 @@
         <v>2024</v>
       </c>
       <c r="D21" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>32</v>
@@ -13450,9 +13565,9 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B22" s="5">
         <v>3.406828703703704E-3</v>
@@ -13461,7 +13576,7 @@
         <v>2023</v>
       </c>
       <c r="D22" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>132</v>
@@ -13473,7 +13588,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>93</v>
       </c>
@@ -13484,7 +13599,7 @@
         <v>2022</v>
       </c>
       <c r="D23" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>109</v>
@@ -13496,7 +13611,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>153</v>
       </c>
@@ -13507,7 +13622,7 @@
         <v>2024</v>
       </c>
       <c r="D24" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F24" s="13" t="s">
         <v>132</v>
@@ -13519,9 +13634,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B25" s="12">
         <v>3.4240740740740746E-3</v>
@@ -13530,10 +13645,10 @@
         <v>2026</v>
       </c>
       <c r="D25" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="G25" s="14">
         <v>4.3596064814814817E-3</v>
@@ -13542,7 +13657,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>102</v>
       </c>
@@ -13553,10 +13668,10 @@
         <v>2024</v>
       </c>
       <c r="D26" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>77</v>
       </c>
@@ -13567,7 +13682,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>191</v>
       </c>
@@ -13578,10 +13693,10 @@
         <v>2021</v>
       </c>
       <c r="D28" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>158</v>
       </c>
@@ -13592,10 +13707,10 @@
         <v>2021</v>
       </c>
       <c r="D29" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>88</v>
       </c>
@@ -13606,7 +13721,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>181</v>
       </c>
@@ -13617,7 +13732,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>153</v>
       </c>
@@ -13628,10 +13743,10 @@
         <v>2023</v>
       </c>
       <c r="D32" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>47</v>
       </c>
@@ -13642,10 +13757,10 @@
         <v>2026</v>
       </c>
       <c r="D33" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>153</v>
       </c>
@@ -13656,7 +13771,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>167</v>
       </c>
@@ -13667,7 +13782,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>167</v>
       </c>
@@ -13678,7 +13793,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>106</v>
       </c>
@@ -13689,7 +13804,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>99</v>
       </c>
@@ -13700,7 +13815,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>186</v>
       </c>
@@ -13711,10 +13826,10 @@
         <v>2023</v>
       </c>
       <c r="D39" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>123</v>
       </c>
@@ -13725,7 +13840,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>173</v>
       </c>
@@ -13736,7 +13851,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>39</v>
       </c>
@@ -13747,7 +13862,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>196</v>
       </c>
@@ -13758,7 +13873,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>88</v>
       </c>
@@ -13769,10 +13884,10 @@
         <v>2023</v>
       </c>
       <c r="D44" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>31</v>
       </c>
@@ -13783,7 +13898,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
         <v>39</v>
       </c>
@@ -13794,7 +13909,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>159</v>
       </c>
@@ -13805,10 +13920,10 @@
         <v>2021</v>
       </c>
       <c r="D47" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
         <v>75</v>
       </c>
@@ -13819,7 +13934,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>170</v>
       </c>
@@ -13830,10 +13945,10 @@
         <v>2023</v>
       </c>
       <c r="D49" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>3</v>
       </c>
@@ -13844,7 +13959,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
         <v>171</v>
       </c>
@@ -13855,7 +13970,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>181</v>
       </c>
@@ -13866,10 +13981,10 @@
         <v>2023</v>
       </c>
       <c r="D52" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="11" t="s">
         <v>156</v>
       </c>
@@ -13880,7 +13995,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>99</v>
       </c>
@@ -13891,7 +14006,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>166</v>
       </c>
@@ -13902,7 +14017,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>98</v>
       </c>
@@ -13913,7 +14028,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>166</v>
       </c>
@@ -13924,7 +14039,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>90</v>
       </c>
@@ -13935,10 +14050,10 @@
         <v>2021</v>
       </c>
       <c r="D58" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>39</v>
       </c>
@@ -13949,7 +14064,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="11" t="s">
         <v>177</v>
       </c>
@@ -13960,7 +14075,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>103</v>
       </c>
@@ -13971,7 +14086,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>167</v>
       </c>
@@ -13982,7 +14097,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="11" t="s">
         <v>134</v>
       </c>
@@ -13993,7 +14108,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>180</v>
       </c>
@@ -14004,10 +14119,10 @@
         <v>2021</v>
       </c>
       <c r="D64" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>181</v>
       </c>
@@ -14018,7 +14133,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>100</v>
       </c>
@@ -14029,7 +14144,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>185</v>
       </c>
@@ -14040,7 +14155,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>135</v>
       </c>
@@ -14051,7 +14166,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>145</v>
       </c>
@@ -14062,7 +14177,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>14</v>
       </c>
@@ -14073,7 +14188,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>145</v>
       </c>
@@ -14084,7 +14199,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>145</v>
       </c>
@@ -14095,7 +14210,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>192</v>
       </c>
@@ -14106,7 +14221,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>143</v>
       </c>
@@ -14117,7 +14232,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>195</v>
       </c>
@@ -14128,7 +14243,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
         <v>133</v>
       </c>
@@ -14139,7 +14254,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" s="11" t="s">
         <v>31</v>
       </c>
@@ -14150,7 +14265,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="11" t="s">
         <v>185</v>
       </c>
@@ -14161,7 +14276,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>45</v>
       </c>
@@ -14172,7 +14287,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>179</v>
       </c>
@@ -14183,7 +14298,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>134</v>
       </c>
@@ -14194,7 +14309,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" s="11" t="s">
         <v>14</v>
       </c>
@@ -14205,7 +14320,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>159</v>
       </c>
@@ -14216,7 +14331,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>95</v>
       </c>
@@ -14227,7 +14342,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>202</v>
       </c>
@@ -14238,7 +14353,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>38</v>
       </c>
@@ -14249,7 +14364,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>187</v>
       </c>
@@ -14260,7 +14375,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>178</v>
       </c>
@@ -14271,9 +14386,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="B89" s="5">
         <v>3.8018518518518523E-3</v>
@@ -14282,7 +14397,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>192</v>
       </c>
@@ -14293,7 +14408,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>98</v>
       </c>
@@ -14304,7 +14419,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>199</v>
       </c>
@@ -14315,7 +14430,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>185</v>
       </c>
@@ -14326,7 +14441,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>148</v>
       </c>
@@ -14337,7 +14452,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>159</v>
       </c>
@@ -14348,7 +14463,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>213</v>
       </c>
@@ -14359,7 +14474,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>205</v>
       </c>
@@ -14370,7 +14485,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>184</v>
       </c>
@@ -14381,7 +14496,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="11" t="s">
         <v>193</v>
       </c>
@@ -14392,7 +14507,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>205</v>
       </c>
@@ -14403,7 +14518,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>206</v>
       </c>
@@ -14414,9 +14529,9 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B102" s="5">
         <v>4.0037037037037038E-3</v>
@@ -14425,7 +14540,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>199</v>
       </c>
@@ -14436,9 +14551,9 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="B104" s="5">
         <v>4.0429398148148152E-3</v>
@@ -14447,7 +14562,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="11" t="s">
         <v>206</v>
       </c>
@@ -14458,7 +14573,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="11" t="s">
         <v>62</v>
       </c>
@@ -14469,12 +14584,12 @@
         <v>2026</v>
       </c>
       <c r="D106" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B107" s="5">
         <v>4.1284722222222217E-3</v>
@@ -14483,7 +14598,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>66</v>
       </c>
@@ -14494,10 +14609,10 @@
         <v>2024</v>
       </c>
       <c r="D108" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>68</v>
       </c>
@@ -14508,10 +14623,10 @@
         <v>2023</v>
       </c>
       <c r="D109" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>64</v>
       </c>
@@ -14522,10 +14637,10 @@
         <v>2023</v>
       </c>
       <c r="D110" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>46</v>
       </c>
@@ -14536,10 +14651,10 @@
         <v>2023</v>
       </c>
       <c r="D111" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>74</v>
       </c>
@@ -14550,12 +14665,12 @@
         <v>2024</v>
       </c>
       <c r="D112" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B113" s="5">
         <v>4.2732638888888889E-3</v>
@@ -14564,7 +14679,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>78</v>
       </c>
@@ -14575,12 +14690,12 @@
         <v>2025</v>
       </c>
       <c r="D114" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" s="11" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B115" s="12">
         <v>4.2856481481481478E-3</v>
@@ -14589,7 +14704,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>72</v>
       </c>
@@ -14600,10 +14715,10 @@
         <v>2024</v>
       </c>
       <c r="D116" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
         <v>28</v>
       </c>
@@ -14614,12 +14729,12 @@
         <v>2026</v>
       </c>
       <c r="D117" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B118" s="5">
         <v>4.3806712962962966E-3</v>
@@ -14628,10 +14743,10 @@
         <v>2021</v>
       </c>
       <c r="D118" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" s="11" t="s">
         <v>60</v>
       </c>
@@ -14642,10 +14757,10 @@
         <v>2026</v>
       </c>
       <c r="D119" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" s="11" t="s">
         <v>105</v>
       </c>
@@ -14656,12 +14771,12 @@
         <v>2026</v>
       </c>
       <c r="D120" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="B121" s="12">
         <v>4.4145833333333337E-3</v>
@@ -14670,10 +14785,10 @@
         <v>2026</v>
       </c>
       <c r="D121" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" s="11" t="s">
         <v>87</v>
       </c>
@@ -14684,10 +14799,10 @@
         <v>2026</v>
       </c>
       <c r="D122" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>136</v>
       </c>
@@ -14698,10 +14813,10 @@
         <v>2024</v>
       </c>
       <c r="D123" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>80</v>
       </c>
@@ -14712,10 +14827,10 @@
         <v>2023</v>
       </c>
       <c r="D124" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>72</v>
       </c>
@@ -14726,10 +14841,10 @@
         <v>2025</v>
       </c>
       <c r="D125" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>84</v>
       </c>
@@ -14740,12 +14855,12 @@
         <v>2024</v>
       </c>
       <c r="D126" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" s="11" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B127" s="12">
         <v>4.4717592592592595E-3</v>
@@ -14754,12 +14869,12 @@
         <v>2026</v>
       </c>
       <c r="D127" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B128" s="5">
         <v>4.5248842592592589E-3</v>
@@ -14768,10 +14883,10 @@
         <v>2021</v>
       </c>
       <c r="D128" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>89</v>
       </c>
@@ -14782,10 +14897,10 @@
         <v>2021</v>
       </c>
       <c r="D129" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
         <v>6</v>
       </c>
@@ -14796,7 +14911,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="11" t="s">
         <v>254</v>
       </c>
@@ -14807,7 +14922,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="11" t="s">
         <v>255</v>
       </c>
@@ -14818,7 +14933,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="11" t="s">
         <v>120</v>
       </c>
@@ -14829,7 +14944,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>126</v>
       </c>
@@ -14840,10 +14955,10 @@
         <v>2025</v>
       </c>
       <c r="D134" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>124</v>
       </c>
@@ -14854,10 +14969,10 @@
         <v>2024</v>
       </c>
       <c r="D135" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>120</v>
       </c>
@@ -14868,10 +14983,10 @@
         <v>2025</v>
       </c>
       <c r="D136" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>111</v>
       </c>
@@ -14882,10 +14997,10 @@
         <v>2025</v>
       </c>
       <c r="D137" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>118</v>
       </c>
@@ -14896,10 +15011,10 @@
         <v>2021</v>
       </c>
       <c r="D138" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>136</v>
       </c>
@@ -14910,10 +15025,10 @@
         <v>2023</v>
       </c>
       <c r="D139" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>117</v>
       </c>
@@ -14924,10 +15039,10 @@
         <v>2025</v>
       </c>
       <c r="D140" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>115</v>
       </c>
@@ -14938,12 +15053,12 @@
         <v>2021</v>
       </c>
       <c r="D141" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B142" s="5">
         <v>4.9483796296296298E-3</v>
@@ -14952,10 +15067,10 @@
         <v>2021</v>
       </c>
       <c r="D142" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>107</v>
       </c>
@@ -14966,12 +15081,12 @@
         <v>2021</v>
       </c>
       <c r="D143" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B144" s="12">
         <v>4.977199074074074E-3</v>
@@ -14980,7 +15095,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>186</v>
       </c>
@@ -14991,9 +15106,9 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B146" s="5">
         <v>5.0518518518518516E-3</v>
@@ -15002,10 +15117,10 @@
         <v>2024</v>
       </c>
       <c r="D146" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>10</v>
       </c>
@@ -15016,10 +15131,10 @@
         <v>2025</v>
       </c>
       <c r="D147" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>124</v>
       </c>
@@ -15030,12 +15145,12 @@
         <v>2023</v>
       </c>
       <c r="D148" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="B149" s="5">
         <v>5.0864583333333335E-3</v>
@@ -15044,10 +15159,10 @@
         <v>2023</v>
       </c>
       <c r="D149" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>136</v>
       </c>
@@ -15058,7 +15173,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>117</v>
       </c>
@@ -15081,12 +15196,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A42EA60D-212D-4C7E-A10A-59214A8DF03C}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -15097,7 +15212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>169</v>
       </c>
@@ -15108,7 +15223,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
         <v>260</v>
       </c>
@@ -15119,7 +15234,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
         <v>261</v>
       </c>
@@ -15130,7 +15245,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
         <v>156</v>
       </c>
@@ -15141,7 +15256,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
         <v>188</v>
       </c>
@@ -15152,7 +15267,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
         <v>173</v>
       </c>
@@ -15163,7 +15278,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
         <v>262</v>
       </c>
@@ -15174,7 +15289,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>263</v>
       </c>
@@ -15185,7 +15300,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>175</v>
       </c>
@@ -15196,7 +15311,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
         <v>264</v>
       </c>
@@ -15207,7 +15322,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
         <v>123</v>
       </c>
@@ -15218,7 +15333,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
         <v>265</v>
       </c>
@@ -15229,7 +15344,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
         <v>266</v>
       </c>
@@ -15240,7 +15355,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
         <v>267</v>
       </c>
@@ -15251,7 +15366,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>268</v>
       </c>
@@ -15262,7 +15377,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
         <v>193</v>
       </c>
@@ -15273,7 +15388,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
         <v>269</v>
       </c>
@@ -15284,7 +15399,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
         <v>270</v>
       </c>
@@ -15295,7 +15410,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
         <v>133</v>
       </c>
@@ -15306,7 +15421,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
         <v>271</v>
       </c>
@@ -15317,7 +15432,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
         <v>209</v>
       </c>
@@ -15328,7 +15443,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
         <v>272</v>
       </c>
@@ -15339,7 +15454,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
         <v>273</v>
       </c>
@@ -15350,7 +15465,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
         <v>185</v>
       </c>
@@ -15361,7 +15476,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
         <v>206</v>
       </c>
@@ -15372,17 +15487,17 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="18"/>
       <c r="B27" s="15"/>
       <c r="C27" s="18"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="18"/>
       <c r="B28" s="15"/>
       <c r="C28" s="18"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="20"/>
       <c r="B29" s="16"/>
       <c r="C29" s="20"/>
@@ -15396,6 +15511,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="708f94e2-bc9d-47d3-91b0-462b2627b1ab">
+      <UserInfo>
+        <DisplayName>Philip Spitzer</DisplayName>
+        <AccountId>9</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="708f94e2-bc9d-47d3-91b0-462b2627b1ab" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4fe04df2-ace4-48e4-aefd-fb7781d79850">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004AF72C2E85617944A40F2FF337DFE4E9" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7257922ecea9c1614a5cce6092587b33">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="4fe04df2-ace4-48e4-aefd-fb7781d79850" xmlns:ns3="708f94e2-bc9d-47d3-91b0-462b2627b1ab" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="491f6758f9d4bab72c71ad639e010c10" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -15647,26 +15782,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="708f94e2-bc9d-47d3-91b0-462b2627b1ab">
-      <UserInfo>
-        <DisplayName>Philip Spitzer</DisplayName>
-        <AccountId>9</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="708f94e2-bc9d-47d3-91b0-462b2627b1ab" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4fe04df2-ace4-48e4-aefd-fb7781d79850">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -15677,13 +15792,47 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0386B601-E309-4427-A11C-22994F16DB05}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8147BDD-D7F2-4C76-8F94-5CEA8C8E5196}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="708f94e2-bc9d-47d3-91b0-462b2627b1ab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4fe04df2-ace4-48e4-aefd-fb7781d79850"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8147BDD-D7F2-4C76-8F94-5CEA8C8E5196}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0386B601-E309-4427-A11C-22994F16DB05}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4fe04df2-ace4-48e4-aefd-fb7781d79850"/>
+    <ds:schemaRef ds:uri="708f94e2-bc9d-47d3-91b0-462b2627b1ab"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80B0C17E-657A-472F-AB41-DFDC9CA0CFEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80B0C17E-657A-472F-AB41-DFDC9CA0CFEB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>